--- a/data/trans_dic/P19C01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,09; 26,84</t>
+          <t>19,24; 26,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,75; 25,5</t>
+          <t>18,73; 25,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,6; 38,91</t>
+          <t>31,17; 39,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,69; 55,84</t>
+          <t>46,72; 55,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 30,09</t>
+          <t>22,67; 29,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,44; 36,08</t>
+          <t>28,79; 36,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,1; 44,27</t>
+          <t>35,69; 44,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,8; 55,9</t>
+          <t>49,83; 55,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 27,62</t>
+          <t>22,04; 27,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,79; 29,92</t>
+          <t>24,7; 29,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,49; 40,73</t>
+          <t>34,9; 40,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,17; 54,79</t>
+          <t>49,06; 54,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,29; 33,44</t>
+          <t>26,54; 33,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,39; 33,13</t>
+          <t>26,59; 33,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,17; 44,06</t>
+          <t>37,23; 44,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,24; 60,6</t>
+          <t>25,74; 60,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,26; 36,13</t>
+          <t>29,59; 36,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,04; 36,77</t>
+          <t>30,03; 36,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,8; 44,59</t>
+          <t>37,84; 44,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,62; 64,1</t>
+          <t>58,57; 64,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,0; 33,81</t>
+          <t>29,27; 33,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,38; 33,9</t>
+          <t>29,08; 33,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,54; 43,39</t>
+          <t>38,28; 43,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,27; 61,03</t>
+          <t>33,22; 61,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,75; 32,64</t>
+          <t>24,75; 32,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,03; 35,89</t>
+          <t>28,11; 36,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,79; 43,57</t>
+          <t>34,58; 43,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,15; 59,11</t>
+          <t>50,15; 58,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,35; 31,31</t>
+          <t>24,36; 31,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,84; 36,47</t>
+          <t>28,91; 36,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,67; 47,04</t>
+          <t>38,74; 46,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 53,68</t>
+          <t>19,31; 53,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,38; 30,94</t>
+          <t>25,6; 31,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,52; 34,93</t>
+          <t>29,61; 34,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,03; 44,02</t>
+          <t>37,91; 43,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,78; 54,57</t>
+          <t>27,9; 54,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,62; 38,75</t>
+          <t>31,55; 38,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,38; 36,13</t>
+          <t>29,23; 36,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,41; 49,76</t>
+          <t>42,67; 49,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,75; 65,61</t>
+          <t>58,56; 65,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,69; 39,41</t>
+          <t>32,56; 39,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,55; 40,96</t>
+          <t>34,5; 41,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,41; 51,7</t>
+          <t>44,6; 51,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,43; 73,4</t>
+          <t>62,75; 73,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,96; 37,79</t>
+          <t>33,13; 38,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,97; 37,65</t>
+          <t>33,06; 37,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44,34; 49,5</t>
+          <t>44,5; 49,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,66; 68,36</t>
+          <t>61,92; 68,93</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,17; 31,6</t>
+          <t>27,99; 31,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,58; 31,25</t>
+          <t>27,78; 31,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,95; 42,93</t>
+          <t>38,77; 42,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,03; 58,15</t>
+          <t>41,74; 58,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 33,38</t>
+          <t>29,71; 33,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,54; 36,01</t>
+          <t>32,55; 35,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,56; 45,32</t>
+          <t>41,61; 45,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,31; 60,07</t>
+          <t>44,37; 60,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,41; 31,95</t>
+          <t>29,36; 31,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,56; 33,11</t>
+          <t>30,74; 33,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,75; 43,45</t>
+          <t>40,83; 43,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,86; 58,51</t>
+          <t>48,01; 57,99</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91211; 128261</t>
+          <t>91938; 128897</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113616; 154529</t>
+          <t>113523; 155044</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160637; 204278</t>
+          <t>163651; 205085</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>285397; 341364</t>
+          <t>285618; 339701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>122943; 161926</t>
+          <t>121995; 159403</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>180830; 229410</t>
+          <t>183074; 231671</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>196503; 240977</t>
+          <t>194306; 241899</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>324482; 364191</t>
+          <t>324689; 364709</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>225264; 280648</t>
+          <t>223956; 278838</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>307847; 371557</t>
+          <t>306717; 371181</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>368809; 435504</t>
+          <t>373189; 436954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>620947; 691943</t>
+          <t>619547; 690720</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>189831; 241465</t>
+          <t>191647; 241109</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>228771; 287253</t>
+          <t>230562; 286305</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303452; 359651</t>
+          <t>303922; 360603</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>283013; 707417</t>
+          <t>300437; 709114</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>235301; 290580</t>
+          <t>237997; 294580</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>270001; 330491</t>
+          <t>269948; 325016</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>327463; 386317</t>
+          <t>327808; 388669</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>552352; 604009</t>
+          <t>551884; 605751</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>442575; 516044</t>
+          <t>446828; 514448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>518878; 598587</t>
+          <t>513574; 595118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>648500; 730050</t>
+          <t>644144; 727692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>723072; 1287547</t>
+          <t>700911; 1289358</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>134884; 177905</t>
+          <t>134895; 177069</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>178278; 228247</t>
+          <t>178775; 229198</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>191449; 239769</t>
+          <t>190313; 239244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344157; 405685</t>
+          <t>344188; 404628</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>142356; 183054</t>
+          <t>142409; 184831</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>195410; 247079</t>
+          <t>195855; 246031</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>224196; 272703</t>
+          <t>224592; 272127</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>166553; 494956</t>
+          <t>178070; 495527</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>286762; 349580</t>
+          <t>289238; 352484</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>387804; 458797</t>
+          <t>388977; 459174</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>429784; 497459</t>
+          <t>428440; 495708</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>430777; 877681</t>
+          <t>448740; 874556</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>224910; 275566</t>
+          <t>224382; 275620</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>236740; 291057</t>
+          <t>235476; 293045</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>327673; 384435</t>
+          <t>329651; 384758</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>522867; 583860</t>
+          <t>521182; 585332</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>265830; 320468</t>
+          <t>264735; 322481</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>322382; 382263</t>
+          <t>321959; 385241</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>389430; 453327</t>
+          <t>391104; 450248</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>663585; 780170</t>
+          <t>667022; 778286</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>502392; 575982</t>
+          <t>505008; 581424</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>573347; 654745</t>
+          <t>574810; 654136</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>731409; 816474</t>
+          <t>734008; 816655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1204215; 1334932</t>
+          <t>1209169; 1346193</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>692031; 776288</t>
+          <t>687407; 777003</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>803968; 910699</t>
+          <t>809706; 913371</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1037677; 1143813</t>
+          <t>1032978; 1137089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1376402; 1951046</t>
+          <t>1400399; 1951534</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>813224; 914498</t>
+          <t>813931; 907265</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1023560; 1132517</t>
+          <t>1023692; 1131777</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1191683; 1299392</t>
+          <t>1193046; 1302499</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1585742; 2149709</t>
+          <t>1587861; 2147506</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1528215; 1660205</t>
+          <t>1525596; 1658507</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1851991; 2006171</t>
+          <t>1863103; 2017148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2254138; 2403527</t>
+          <t>2258370; 2401253</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3318150; 4056925</t>
+          <t>3328718; 4020537</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,24; 26,98</t>
+          <t>19,49; 27,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,73; 25,59</t>
+          <t>18,49; 25,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,17; 39,06</t>
+          <t>30,92; 39,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,72; 55,57</t>
+          <t>46,38; 54,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,67; 29,62</t>
+          <t>22,89; 30,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,79; 36,44</t>
+          <t>29,03; 36,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,69; 44,44</t>
+          <t>35,8; 44,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,83; 55,98</t>
+          <t>49,83; 56,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,04; 27,45</t>
+          <t>22,03; 27,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,7; 29,89</t>
+          <t>24,74; 30,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,9; 40,86</t>
+          <t>34,31; 40,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,06; 54,7</t>
+          <t>49,34; 54,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,54; 33,39</t>
+          <t>26,44; 33,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,59; 33,02</t>
+          <t>26,44; 33,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,23; 44,17</t>
+          <t>37,5; 44,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,74; 60,74</t>
+          <t>56,15; 63,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,59; 36,63</t>
+          <t>29,41; 35,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,03; 36,16</t>
+          <t>30,04; 36,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,84; 44,86</t>
+          <t>37,63; 44,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,57; 64,28</t>
+          <t>59,29; 64,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,27; 33,7</t>
+          <t>28,89; 33,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,08; 33,7</t>
+          <t>29,29; 33,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,28; 43,25</t>
+          <t>38,74; 43,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,22; 61,11</t>
+          <t>58,65; 62,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,75; 32,48</t>
+          <t>24,94; 32,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,11; 36,04</t>
+          <t>28,18; 35,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,58; 43,47</t>
+          <t>34,7; 43,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,15; 58,96</t>
+          <t>49,78; 57,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,36; 31,62</t>
+          <t>24,39; 31,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,91; 36,31</t>
+          <t>29,06; 36,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,74; 46,94</t>
+          <t>38,78; 46,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,31; 53,74</t>
+          <t>51,48; 58,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,6; 31,2</t>
+          <t>25,64; 30,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,61; 34,96</t>
+          <t>29,48; 35,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,91; 43,86</t>
+          <t>37,85; 44,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,9; 54,38</t>
+          <t>51,82; 57,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,55; 38,75</t>
+          <t>31,33; 38,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,23; 36,37</t>
+          <t>29,73; 36,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,67; 49,8</t>
+          <t>42,77; 49,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,56; 65,77</t>
+          <t>58,14; 64,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,56; 39,66</t>
+          <t>32,9; 39,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,5; 41,28</t>
+          <t>34,45; 40,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,6; 51,35</t>
+          <t>44,52; 51,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,75; 73,22</t>
+          <t>61,15; 66,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,13; 38,14</t>
+          <t>33,28; 37,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,06; 37,62</t>
+          <t>32,97; 37,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44,5; 49,51</t>
+          <t>44,63; 49,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,92; 68,93</t>
+          <t>60,46; 64,74</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,99; 31,63</t>
+          <t>27,98; 31,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,78; 31,34</t>
+          <t>27,62; 31,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,77; 42,68</t>
+          <t>38,88; 42,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41,74; 58,17</t>
+          <t>55,08; 58,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,71; 33,11</t>
+          <t>29,66; 33,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,55; 35,98</t>
+          <t>32,42; 36,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,61; 45,43</t>
+          <t>41,39; 45,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,37; 60,01</t>
+          <t>57,68; 60,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,36; 31,92</t>
+          <t>29,28; 31,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,74; 33,29</t>
+          <t>30,77; 33,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,83; 43,41</t>
+          <t>40,78; 43,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,01; 57,99</t>
+          <t>56,82; 59,28</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312163</t>
+          <t>332643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>344669</t>
+          <t>374162</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>656832</t>
+          <t>706804</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91938; 128897</t>
+          <t>93150; 129108</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113523; 155044</t>
+          <t>112024; 153800</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163651; 205085</t>
+          <t>162337; 206787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>285618; 339701</t>
+          <t>305901; 360480</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>121995; 159403</t>
+          <t>123178; 165484</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>183074; 231671</t>
+          <t>184589; 231313</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>194306; 241899</t>
+          <t>194905; 239801</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>324689; 364709</t>
+          <t>351901; 396253</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>223956; 278838</t>
+          <t>223764; 282217</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>306717; 371181</t>
+          <t>307267; 373342</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>373189; 436954</t>
+          <t>366849; 430650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>619547; 690720</t>
+          <t>673810; 744970</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>550276</t>
+          <t>605649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>577991</t>
+          <t>648119</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1128267</t>
+          <t>1253768</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>191647; 241109</t>
+          <t>190960; 243576</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>230562; 286305</t>
+          <t>229225; 288307</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303922; 360603</t>
+          <t>306092; 362743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>300437; 709114</t>
+          <t>571164; 643583</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>237997; 294580</t>
+          <t>236546; 289051</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>269948; 325016</t>
+          <t>270027; 328023</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>327808; 388669</t>
+          <t>326003; 386441</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>551884; 605751</t>
+          <t>621266; 674606</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446828; 514448</t>
+          <t>440985; 518058</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513574; 595118</t>
+          <t>517183; 597595</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>644144; 727692</t>
+          <t>651946; 730155</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>700911; 1289358</t>
+          <t>1211017; 1296046</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>374875</t>
+          <t>418344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>373062</t>
+          <t>436331</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>747937</t>
+          <t>854675</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>134895; 177069</t>
+          <t>135926; 179199</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>178775; 229198</t>
+          <t>179211; 228365</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190313; 239244</t>
+          <t>190956; 236845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344188; 404628</t>
+          <t>385317; 446952</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>142409; 184831</t>
+          <t>142572; 183807</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>195855; 246031</t>
+          <t>196906; 247384</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>224592; 272127</t>
+          <t>224837; 270970</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>178070; 495527</t>
+          <t>409457; 463521</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>289238; 352484</t>
+          <t>289634; 350103</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>388977; 459174</t>
+          <t>387200; 459809</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>428440; 495708</t>
+          <t>427691; 497236</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>448740; 874556</t>
+          <t>813162; 894555</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>553896</t>
+          <t>582694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>702120</t>
+          <t>685185</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1256015</t>
+          <t>1267879</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>224382; 275620</t>
+          <t>222811; 270880</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>235476; 293045</t>
+          <t>239552; 293628</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>329651; 384758</t>
+          <t>330444; 385863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>521182; 585332</t>
+          <t>551187; 612711</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>264735; 322481</t>
+          <t>267471; 321179</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>321959; 385241</t>
+          <t>321462; 381038</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>391104; 450248</t>
+          <t>390372; 452002</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>667022; 778286</t>
+          <t>658082; 712342</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>505008; 581424</t>
+          <t>507290; 578865</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>574810; 654136</t>
+          <t>573226; 656306</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>734008; 816655</t>
+          <t>736106; 817383</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1209169; 1346193</t>
+          <t>1223783; 1310516</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1791211</t>
+          <t>1939330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1997841</t>
+          <t>2143796</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3789051</t>
+          <t>4083126</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>687407; 777003</t>
+          <t>687219; 780082</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>809706; 913371</t>
+          <t>805087; 907853</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1032978; 1137089</t>
+          <t>1035993; 1135352</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1400399; 1951534</t>
+          <t>1872035; 2002868</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>813931; 907265</t>
+          <t>812786; 908419</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1023692; 1131777</t>
+          <t>1019742; 1132844</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1193046; 1302499</t>
+          <t>1186673; 1299243</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1587861; 2147506</t>
+          <t>2091003; 2197801</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1525596; 1658507</t>
+          <t>1521653; 1660640</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1863103; 2017148</t>
+          <t>1864483; 2018008</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2258370; 2401253</t>
+          <t>2255915; 2411091</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3328718; 4020537</t>
+          <t>3990974; 4163549</t>
         </is>
       </c>
     </row>
